--- a/decks/ayoub/keyword-research.xlsx
+++ b/decks/ayoub/keyword-research.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,13 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +58,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B942"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CC53F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0046AE41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00c9a227"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004a6fc2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002c4a8c"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -92,6 +127,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,57 +533,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Article Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Primary Keyword</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -550,12 +609,12 @@
       <c r="E2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -580,49 +639,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>How to Clean a Persian Rug Without Damaging It</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>how to clean persian rug</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Evergreen care guide — high AI citation potential.</t>
         </is>
@@ -648,12 +707,12 @@
       <c r="E4" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -678,49 +737,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Is Steam Cleaning Safe for Oriental Rugs?</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>steam cleaning oriental rugs</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>AI-answer format. Common homeowner question.</t>
         </is>
@@ -746,12 +805,12 @@
       <c r="E6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -776,49 +835,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Antique Rug Cleaning: Preserving Value While Removing Dirt</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>antique rug cleaning</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Estate-home audience. High trust required — perfect for Ayoub.</t>
         </is>
@@ -844,12 +903,12 @@
       <c r="E8" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -869,49 +928,49 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>How to Remove Pet Stains from a Persian Rug</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>pet stains persian rug</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>AEO content — AI models cite this type heavily.</t>
         </is>
@@ -937,12 +996,12 @@
       <c r="E10" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -967,49 +1026,49 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Rug Cleaners Near Me: What to Expect from a Professional Service</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>rug cleaners near me</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>GSC: pos 7.9 — near page-1, needs content support.</t>
         </is>
@@ -1035,12 +1094,12 @@
       <c r="E12" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -1065,49 +1124,48 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Rug Cleaning Rockville MD: Drop-Off &amp; Pickup Available</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>rug cleaning rockville md</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1129,12 +1187,12 @@
       <c r="E14" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -1159,49 +1217,48 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>How Often Should You Clean Your Carpet? (Room-by-Room Guide)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>how often carpet cleaning</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1223,12 +1280,12 @@
       <c r="E16" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -1253,49 +1310,49 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Rug Cleaning Near Me: 5 Questions to Ask Before Booking</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>rug cleaning near me</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>GSC: pos 9.4 — one optimization push from top 5.</t>
         </is>
@@ -1321,12 +1378,12 @@
       <c r="E18" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -1346,49 +1403,49 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Navajo &amp; Tribal Rug Cleaning: Preserving Cultural Textiles</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>navajo rug cleaning</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Niche specialty — differentiator from franchise chains.</t>
         </is>
@@ -1414,12 +1471,12 @@
       <c r="E20" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -1444,49 +1501,49 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Upholstery Cleaning Guide: Sofas, Chairs, and Sectionals</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>upholstery cleaning</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Pillar hub for upholstery cluster.</t>
         </is>
@@ -1512,12 +1569,12 @@
       <c r="E22" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -1537,49 +1594,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Best Carpet Cleaner in Rockville MD: Why Homeowners Choose Ayoub</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>best carpet cleaner rockville md</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1601,12 +1657,12 @@
       <c r="E24" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -1626,49 +1682,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Tile &amp; Grout Cleaning: Before and After Guide for Maryland Homeowners</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>tile grout cleaning</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Specialty service — no meaningful franchise competition.</t>
         </is>
@@ -1694,12 +1750,12 @@
       <c r="E26" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -1724,49 +1780,48 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Microfiber Upholstery Cleaning: Safe Methods and What to Avoid</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>microfiber upholstery cleaning</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1788,12 +1843,12 @@
       <c r="E28" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -1818,49 +1873,48 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Professional Drapery Cleaning vs DIY: An Honest Comparison</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>professional drapery cleaning</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1882,12 +1936,12 @@
       <c r="E30" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -1907,49 +1961,48 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Leather Upholstery Cleaning: A Specialist's Care Guide</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>leather upholstery cleaning</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1971,12 +2024,12 @@
       <c r="E32" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -2001,49 +2054,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>What Chemicals Are Used in Carpet Cleaning? (Safe for Kids &amp; Pets)</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>carpet cleaning chemicals safe</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Trust-builder — estate-home owners care deeply about this.</t>
         </is>
@@ -2069,12 +2122,12 @@
       <c r="E34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -2099,49 +2152,48 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Rug Odor Removal: How to Get Rid of Pet, Mildew, and Musty Smells</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>rug odor removal</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2163,12 +2215,12 @@
       <c r="E36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -2193,49 +2245,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Carpet Cleaning Bethesda MD: Professional Service Near You</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>carpet cleaning bethesda md</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>GSC shows rug cleaning bethesda pos 12.2 — strong demand signal.</t>
         </is>
@@ -2261,12 +2313,12 @@
       <c r="E38" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -2291,49 +2343,49 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Rug Cleaning Bethesda MD: What Homeowners Should Know</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>rug cleaning bethesda</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>GSC: pos 12.2 — one page from top 5.</t>
         </is>
@@ -2359,12 +2411,12 @@
       <c r="E40" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -2389,49 +2441,49 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Rug Cleaning Washington DC: In-Plant Service for Area Homeowners</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>rug cleaning washington dc</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>GSC: pos 11.6 for 'rug cleaning washington'.</t>
         </is>
@@ -2457,12 +2509,12 @@
       <c r="E42" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -2482,49 +2534,48 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hardwood Floor Refinishing Cost in Maryland: 2026 Price Guide</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>hardwood floor refinishing cost maryland</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2546,12 +2597,12 @@
       <c r="E44" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -2571,49 +2622,48 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>How to Clean a Kilim Rug: Flat-Weave Specific Methods</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>how to clean kilim rug</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2635,12 +2685,12 @@
       <c r="E46" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -2660,49 +2710,48 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Shag Rug Cleaning: How to Clean High-Pile Without Matting</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>shag rug cleaning</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="J47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2724,12 +2773,12 @@
       <c r="E48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -2749,49 +2798,48 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Carpet Cleaning Prices Explained: What You're Really Paying For</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>carpet cleaning prices</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2813,12 +2861,12 @@
       <c r="E50" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -2838,49 +2886,48 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Upholstery Cleaning Cost in Maryland: 2026 Price Guide</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>upholstery cleaning cost</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2902,12 +2949,12 @@
       <c r="E52" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -2927,49 +2974,49 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Velvet Drape Cleaning: What a Professional Does That DIY Can't</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>velvet drape cleaning</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="J53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Estate-home specialty.</t>
         </is>
@@ -2995,12 +3042,12 @@
       <c r="E54" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -3020,49 +3067,48 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Rug Cleaning Germantown MD: What to Expect</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>rug cleaning germantown md</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="J55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3084,12 +3130,12 @@
       <c r="E56" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -3114,49 +3160,48 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Rug Padding Guide: How It Affects Cleaning Frequency</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>rug pad cleaning</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3178,12 +3223,12 @@
       <c r="E58" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -3203,49 +3248,48 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>How to Clean a Jute Rug Without Shrinking or Warping It</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>how to clean jute rug</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3267,12 +3311,12 @@
       <c r="E60" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -3292,49 +3336,48 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Carpet Stain Removal Guide: Every Type of Stain Covered</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>carpet stain removal</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3356,12 +3399,12 @@
       <c r="E62" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -3381,49 +3424,49 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>How to Clean a Cowhide Rug</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>how to clean cowhide rug</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -3449,12 +3492,12 @@
       <c r="E64" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -3474,49 +3517,49 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>How to Care for a Vintage Wool Rug: Expert Advice</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>vintage wool rug care</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>High E-E-A-T potential.</t>
         </is>
@@ -3542,12 +3585,12 @@
       <c r="E66" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -3567,49 +3610,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Ayoub N&amp;H vs Stanley Steemer: An Honest Comparison for MD Homeowners</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>stanley steemer alternative maryland</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Competitor comparison — captures decision-stage searchers. Addresses 'country squire cleaners' rank confusion.</t>
         </is>
@@ -3635,12 +3678,12 @@
       <c r="E68" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -3665,49 +3708,49 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Rug Cleaning Potomac MD: White-Glove Pickup for Estate Homes</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>rug cleaning potomac md</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="J69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>High-income ZIP — estate home audience.</t>
         </is>
@@ -3733,12 +3776,12 @@
       <c r="E70" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -3758,49 +3801,49 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Best Rug Cleaner in Rockville MD: Why Homeowners Choose Ayoub</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>best rug cleaner rockville md</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J71" s="4" t="n">
+      <c r="J71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Reputation content.</t>
         </is>
@@ -3826,12 +3869,12 @@
       <c r="E72" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -3856,49 +3899,48 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Hardwood Floor Refinishing Cost in the DMV: What to Budget</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>hardwood refinishing cost dmv</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="J73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3920,12 +3962,12 @@
       <c r="E74" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -3950,49 +3992,49 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>What's the Best Way to Clean an Oriental Rug? (Expert Answer)</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>best way to clean oriental rug</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>AI-answer format.</t>
         </is>
@@ -4018,12 +4060,12 @@
       <c r="E76" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -4048,49 +4090,48 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Drapery Cleaning Kensington MD: In-Home White-Glove Service</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>drapery cleaning kensington md</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J77" s="4" t="n">
+      <c r="J77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4112,12 +4153,12 @@
       <c r="E78" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -4137,49 +4178,48 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Carpet Cleaning North Bethesda MD: Full Service Guide</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>carpet cleaning north bethesda md</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J79" s="4" t="n">
+      <c r="J79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4201,12 +4241,12 @@
       <c r="E80" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -4226,49 +4266,49 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Who Cleans Draperies in the DC Suburbs? (A Practical Guide)</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>drapery cleaning dc suburbs</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="J81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>AEO format — AI search target.</t>
         </is>
@@ -4294,12 +4334,12 @@
       <c r="E82" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -4319,49 +4359,48 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Grout Sealing After Cleaning: Why It Matters and How Long It Lasts</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>grout sealing after cleaning</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -4383,12 +4422,12 @@
       <c r="E84" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -4408,49 +4447,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>How Often Should You Have Draperies Professionally Cleaned?</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>how often clean draperies</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="J85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -4476,12 +4515,12 @@
       <c r="E86" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -4501,49 +4540,49 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Rug Cleaning McLean VA: Serving the Northern Virginia Estate Market</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>rug cleaning mclean va</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Cross-state service area — Ayoub serves VA too.</t>
         </is>
@@ -4569,12 +4608,12 @@
       <c r="E88" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -4594,49 +4633,48 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Rug Cleaning Fairfax VA: Pickup and Delivery to In-Plant Facility</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>rug cleaning fairfax va</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="J89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -4658,12 +4696,12 @@
       <c r="E90" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -4688,49 +4726,49 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>New Construction Carpet Cleaning: Removing Construction Dust</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>new construction carpet cleaning</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="J91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Estate renovation audience.</t>
         </is>
@@ -4756,12 +4794,12 @@
       <c r="E92" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -4781,49 +4819,48 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Carpet Cleaning for Pet Owners: What Changes When You Have Dogs or Cats</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>carpet cleaning pet owners</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="J93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -4845,12 +4882,12 @@
       <c r="E94" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -4875,49 +4912,48 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Rug Repair and Cleaning: What Ayoub Can Fix Before It Gets Worse</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>rug repair and cleaning</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J95" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4939,12 +4975,12 @@
       <c r="E96" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -4964,49 +5000,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Ayoub Carpet Kensington: Everything at the Showroom Explained</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>ayoub carpet kensington</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Branded</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>GSC: pos 17.1 for branded query — page will lift this to #1.</t>
         </is>
@@ -5032,12 +5068,12 @@
       <c r="E98" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -5055,52 +5091,50 @@
       <c r="J98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Rug Cleaning Bethesda MD: Oriental and Persian Rug Specialists</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>rug cleaning bethesda md specialist</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -5122,12 +5156,12 @@
       <c r="E100" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -5145,52 +5179,50 @@
       <c r="J100" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Carpet Cleaning Columbia MD: Howard County Service Guide</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>carpet cleaning columbia md</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n">
+      <c r="J101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -5212,12 +5244,12 @@
       <c r="E102" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -5235,52 +5267,50 @@
       <c r="J102" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Rug Cleaning Alexandria VA: Serving Northern Virginia Estate Homes</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>rug cleaning alexandria va</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -5302,12 +5332,12 @@
       <c r="E104" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -5325,52 +5355,50 @@
       <c r="J104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>How Long Does Carpet Cleaning Take to Dry? (Realistic Timeline)</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>carpet cleaning dry time</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n">
+      <c r="J105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -5392,12 +5420,12 @@
       <c r="E106" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -5415,52 +5443,50 @@
       <c r="J106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Oriental Rug Cleaning Baltimore MD: Serving the Greater Baltimore Area</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>oriental rug cleaning baltimore md</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J107" s="4" t="n">
+      <c r="J107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -5482,12 +5508,12 @@
       <c r="E108" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -5505,52 +5531,50 @@
       <c r="J108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Carpet Cleaning Waldorf MD: Service Guide for Southern Maryland</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>carpet cleaning waldorf md</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -5572,12 +5596,12 @@
       <c r="E110" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -5595,52 +5619,50 @@
       <c r="J110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>How to Remove Ink Stains from Carpet: What Actually Works</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>ink stain carpet removal</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G111" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J111" s="4" t="n">
+      <c r="J111" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5662,12 +5684,12 @@
       <c r="E112" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -5685,52 +5707,50 @@
       <c r="J112" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Rug Cleaning Reston VA: Serving the Northern Virginia Corridor</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>rug cleaning reston va</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
+      <c r="J113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -5752,12 +5772,12 @@
       <c r="E114" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -5775,52 +5795,50 @@
       <c r="J114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Drapery Cleaning Potomac MD: Premium Fabric Care Service</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>drapery cleaning potomac md</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J115" s="4" t="n">
+      <c r="J115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5842,12 +5860,12 @@
       <c r="E116" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -5865,52 +5883,50 @@
       <c r="J116" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Rug Cleaning Tysons VA: Fine Rug Service for Tysons Corridor Residents</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>rug cleaning tysons va</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
+      <c r="J117" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5932,12 +5948,12 @@
       <c r="E118" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G118" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -5955,52 +5971,50 @@
       <c r="J118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Upholstery Cleaning Kensington MD: Fine Furniture Service</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>upholstery cleaning kensington md</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J119" s="4" t="n">
+      <c r="J119" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -6022,12 +6036,12 @@
       <c r="E120" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -6045,52 +6059,50 @@
       <c r="J120" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Rug Cleaning Fairfax VA: Pickup from Fairfax County Homes</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>rug cleaning fairfax county va</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
+      <c r="J121" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6117,42 +6129,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>In Plan?</t>
         </is>
@@ -6170,12 +6182,12 @@
       <c r="C2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -6197,38 +6209,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>carpet cleaning near me</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>27100</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>28</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6246,12 +6258,12 @@
       <c r="C4" t="n">
         <v>24</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -6273,38 +6285,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>area rug cleaning near me</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>5400</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>22</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6322,12 +6334,12 @@
       <c r="C6" t="n">
         <v>28</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -6349,38 +6361,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>upholstery cleaning</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>6600</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6398,12 +6410,12 @@
       <c r="C8" t="n">
         <v>32</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
@@ -6425,38 +6437,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>tile grout cleaning</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" t="n">
         <v>4400</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6474,12 +6486,12 @@
       <c r="C10" t="n">
         <v>22</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
@@ -6501,38 +6513,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>pet odor removal carpet</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" t="n">
         <v>4400</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" t="n">
         <v>18</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Carpet &amp; Upholstery</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6550,12 +6562,12 @@
       <c r="C12" t="n">
         <v>18</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -6577,38 +6589,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>rug cleaning bethesda</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" t="n">
         <v>720</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6626,12 +6638,12 @@
       <c r="C14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -6653,38 +6665,38 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>country squire cleaners</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" t="n">
         <v>590</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Branded</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>No — competitor brand; suppress via site audit</t>
         </is>
@@ -6702,12 +6714,12 @@
       <c r="C16" t="n">
         <v>16</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -6729,38 +6741,38 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>carpet cleaning kensington md</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" t="n">
         <v>390</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6778,12 +6790,12 @@
       <c r="C18" t="n">
         <v>8</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Location Authority</t>
         </is>
@@ -6805,38 +6817,38 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wool rug cleaning</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" t="n">
         <v>2400</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" t="n">
         <v>24</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6854,12 +6866,12 @@
       <c r="C20" t="n">
         <v>16</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
@@ -6881,38 +6893,38 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>persian rug cleaning</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" t="n">
         <v>3600</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" t="n">
         <v>26</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Oriental &amp; Specialty Rugs</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6940,27 +6952,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Reason Category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Why We Excluded It</t>
         </is>
@@ -6990,23 +7002,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>carpet installation</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>22200</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>28</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Wrong service</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ayoub cleans — doesn't install. High volume but sends wrong audience.</t>
         </is>
@@ -7036,23 +7048,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>oriental rug for sale</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>12100</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>22</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Wrong intent</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>E-commerce intent. Drives zero cleaning leads.</t>
         </is>
@@ -7082,23 +7094,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>stanley steemer</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>74000</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>18</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Competitor brand</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Branded search for competitor. Aggressive targeting would require exact-match domain strategy — not worth the investment.</t>
         </is>
@@ -7128,23 +7140,23 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>carpet cleaning machine rental</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" t="n">
         <v>5400</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>DIY intent</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Active intent to DIY — not seeking professional service.</t>
         </is>

--- a/decks/ayoub/keyword-research.xlsx
+++ b/decks/ayoub/keyword-research.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,16 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +98,23 @@
         <fgColor rgb="002c4a8c"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8743C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,11 +127,16 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -149,6 +177,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6115,818 +6182,8152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>In Plan?</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>oriental rug cleaning near me</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>90500</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaning near me</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>49500</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>40500</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaning</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>40500</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>couch cleaning service</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>33100</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaners near me</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>27100</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>carpet steam cleaning</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>27100</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>carpet steam cleaning near me</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>27100</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>18100</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaner near me</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>14800</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>steam cleaner carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>tile and grout cleaning</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>professional carpet washing</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
         <v>5400</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C14" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>furniture cleaning</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>tile cleaning services</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaners near me</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaner company</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaning professional</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>professional carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaners</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaner service</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>commercial carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>steam cleaning services</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaning service</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>area carpet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>commercial carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>carpet shampooing</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>deep cleaning carpet</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>office carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaning companies</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>upholstery cleaning company</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>apartment carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>880</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning professional</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>880</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>professional carpet cleaner near me</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>880</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>professional carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>professional upholstery cleaning company</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>720</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>steam carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>tile &amp; grout cleaning</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>720</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>tile cleaning company</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>carpet upholstery cleaners near me</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>590</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>cleaning furniture</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>commercial rug cleaners</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="n">
+        <v>590</v>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>Oriental &amp; Specialty Rugs</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>couch cleaner near me</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>furniture cleaning service</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>590</v>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>professional upholstery cleaners near me</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>residential carpet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>590</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>same day carpet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>steam carpet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n">
+        <v>590</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaners services</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning quote</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>480</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>carpet steam cleaning services</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>cleaning couch services</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>480</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>furniture cleaning service near me</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>how often should carpets be cleaned</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>480</v>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>residential carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
+          <t>carpet and upholstery cleaners near me</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>390</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaners pet stains</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning steam cleaning</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>390</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>carpet upholstery cleaning</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>commercial carpet cleaners near me</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="n">
+        <v>390</v>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>commercial carpet cleaning companies</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>furniture and upholstery cleaning</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n">
+        <v>390</v>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>professional couch cleaner near me</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H64" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>professional couch cleaning service</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="n">
+        <v>390</v>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>professional steam cleaning</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaners nearby</t>
+        </is>
+      </c>
+      <c r="B67" s="21" t="n">
+        <v>320</v>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning rochester mn</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>carpet clening near me</t>
+        </is>
+      </c>
+      <c r="B69" s="21" t="n">
+        <v>320</v>
+      </c>
+      <c r="C69" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>industrial carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>local carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B71" s="21" t="n">
+        <v>320</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>professional furniture cleaners near me</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>best commercial carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B73" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C73" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G73" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>best company for carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C74" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H74" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleanning</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>carpet stain removal service</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C76" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H76" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>carpet steamers near me</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>carpet upholstery</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C78" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H78" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>cleaner carpet</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>coupons for carpet shampooers</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C80" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D80" s="26" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H80" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>how often should you clean carpet</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>how often to clean carpet</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>pet stain carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C83" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>pet urine carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H84" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>residential carpet cleaner</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>steam clean carpet near me</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C86" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G86" s="17" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>carpet cleaning near me</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>27100</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="H86" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>steam cleaning service</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>sterk carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C88" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H88" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>tile and grout cleaning companies near me</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="n">
+        <v>260</v>
+      </c>
+      <c r="C89" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>tile grout cleaning company</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="C90" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="25" t="inlineStr">
+        <is>
+          <t>Drapery &amp; Specialty</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H90" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>business carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>carpet celaning</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C92" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H92" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>carpet clean service</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C93" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning brighton</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C94" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H94" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning brighton mi</t>
+        </is>
+      </c>
+      <c r="B95" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C95" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning midland tx</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C96" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D96" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H96" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning professionals</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C97" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>chair cleaning</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C98" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H98" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>cleaning commercial carpet</t>
+        </is>
+      </c>
+      <c r="B99" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C99" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>furniture upholstery cleaning near me</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C100" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H100" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>home carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B101" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C101" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>how often should you carpet clean</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D102" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H102" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>professional carpet clean</t>
+        </is>
+      </c>
+      <c r="B103" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="C103" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>sterk carpet cleaning byron center</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="C104" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D104" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H104" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>ann arbor carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B105" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C105" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>brighton cleaners</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C106" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H106" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>caroet cleaners</t>
+        </is>
+      </c>
+      <c r="B107" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C107" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>carpet clean companies</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C108" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H108" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaner business</t>
+        </is>
+      </c>
+      <c r="B109" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C109" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaners for deep cleaning</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C110" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning canton mi</t>
+        </is>
+      </c>
+      <c r="B111" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C111" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D111" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning companies for pet stains</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C112" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D112" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H112" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning novi</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C113" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning rochester</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C114" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D114" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H114" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning sterling heights</t>
+        </is>
+      </c>
+      <c r="B115" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C115" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>carpet.cleaning near me</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C116" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H116" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
+        <is>
+          <t>cleaning carpet company</t>
+        </is>
+      </c>
+      <c r="B117" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C117" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G117" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H117" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>cleaning services carpet</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C118" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H118" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
+        <is>
+          <t>commercial furniture cleaning</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C119" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D119" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G119" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>company for cleaning carpet</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C120" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H120" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>cost to steam clean carpet</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C121" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D121" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>deep carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C122" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H122" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="inlineStr">
+        <is>
+          <t>deep clean couch service</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C123" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D123" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G123" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H123" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>end of tenancy cleaning services</t>
+        </is>
+      </c>
+      <c r="B124" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C124" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D124" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H124" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>furniture care</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C125" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D125" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H125" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>home and carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C126" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H126" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="inlineStr">
+        <is>
+          <t>how often should you clean your carpets</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C127" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D127" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H127" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>midland cleaners</t>
+        </is>
+      </c>
+      <c r="B128" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C128" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D128" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H128" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="inlineStr">
+        <is>
+          <t>one room carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B129" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C129" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="D129" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G129" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H129" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>professional furniture cleaners</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C130" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D130" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H130" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>residential carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B131" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C131" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="D131" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H131" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>residential carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="C132" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H132" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
+        <is>
+          <t>rug steam cleaning service</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C133" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D133" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G133" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H133" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>arpet cleaner</t>
+        </is>
+      </c>
+      <c r="B134" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C134" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H134" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>caroet cleaning near me</t>
+        </is>
+      </c>
+      <c r="B135" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C135" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E135" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G135" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H135" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaber</t>
+        </is>
+      </c>
+      <c r="B136" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C136" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E136" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H136" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaner manufacturers</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C137" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G137" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H137" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaner professional near me</t>
+        </is>
+      </c>
+      <c r="B138" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C138" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E138" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H138" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning carpet</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C139" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D139" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H139" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning coupons near me</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C140" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D140" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E140" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H140" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning for pet urine</t>
+        </is>
+      </c>
+      <c r="B141" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C141" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D141" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G141" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning holland mi</t>
+        </is>
+      </c>
+      <c r="B142" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D142" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E142" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H142" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning jackson ms</t>
+        </is>
+      </c>
+      <c r="B143" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C143" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D143" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G143" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H143" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning meridian ms</t>
+        </is>
+      </c>
+      <c r="B144" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C144" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D144" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E144" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H144" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning promotions</t>
+        </is>
+      </c>
+      <c r="B145" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C145" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D145" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G145" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H145" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning websites</t>
+        </is>
+      </c>
+      <c r="B146" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C146" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G146" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H146" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="inlineStr">
+        <is>
+          <t>carpet clearning near me</t>
+        </is>
+      </c>
+      <c r="B147" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C147" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G147" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H147" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t>couch clean</t>
+        </is>
+      </c>
+      <c r="B148" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C148" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G148" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H148" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="21" t="inlineStr">
+        <is>
+          <t>couch deep cleaning service</t>
+        </is>
+      </c>
+      <c r="B149" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C149" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D149" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F149" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G149" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H149" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>couch dry cleaning</t>
+        </is>
+      </c>
+      <c r="B150" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C150" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G150" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H150" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="21" t="inlineStr">
+        <is>
+          <t>deep cleaning carpet service</t>
+        </is>
+      </c>
+      <c r="B151" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C151" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>furniture clean</t>
+        </is>
+      </c>
+      <c r="B152" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C152" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D152" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F152" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G152" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H152" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="21" t="inlineStr">
+        <is>
+          <t>how often should carpet be cleaned</t>
+        </is>
+      </c>
+      <c r="B153" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C153" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G153" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H153" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>how often should carpets be cleaned professionally</t>
+        </is>
+      </c>
+      <c r="B154" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C154" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D154" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F154" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G154" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H154" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
+          <t>how often should you wash your carpet</t>
+        </is>
+      </c>
+      <c r="B155" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C155" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="D155" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G155" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H155" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>professional furniture cleaner</t>
+        </is>
+      </c>
+      <c r="B156" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C156" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G156" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H156" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="21" t="inlineStr">
+        <is>
+          <t>sofa clean</t>
+        </is>
+      </c>
+      <c r="B157" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C157" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F157" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G157" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H157" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>sofa upholstery cleaning</t>
+        </is>
+      </c>
+      <c r="B158" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="C158" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F158" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G158" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H158" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="21" t="inlineStr">
+        <is>
+          <t>steam clean carpet cleaners</t>
+        </is>
+      </c>
+      <c r="B159" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C159" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D159" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F159" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G159" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H159" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t>best carpet cleaning for pet stains</t>
+        </is>
+      </c>
+      <c r="B160" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C160" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G160" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H160" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="21" t="inlineStr">
+        <is>
+          <t>best professional carpet cleaning service</t>
+        </is>
+      </c>
+      <c r="B161" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C161" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F161" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G161" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H161" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t>book carpet cleaning online</t>
+        </is>
+      </c>
+      <c r="B162" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C162" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F162" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G162" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H162" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="21" t="inlineStr">
+        <is>
+          <t>carpet ckeaning near me</t>
+        </is>
+      </c>
+      <c r="B163" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C163" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F163" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G163" s="21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H163" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="17" t="inlineStr">
+        <is>
+          <t>carpet clean expert</t>
+        </is>
+      </c>
+      <c r="B164" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C164" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F164" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G164" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H164" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaner brighton</t>
+        </is>
+      </c>
+      <c r="B165" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C165" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H165" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaner company near me prices</t>
+        </is>
+      </c>
+      <c r="B166" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C166" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F166" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G166" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H166" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaner.</t>
+        </is>
+      </c>
+      <c r="B167" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C167" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F167" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G167" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H167" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaners brighton mi</t>
+        </is>
+      </c>
+      <c r="B168" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C168" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F168" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G168" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H168" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning a</t>
+        </is>
+      </c>
+      <c r="B169" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C169" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F169" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H169" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning canton</t>
+        </is>
+      </c>
+      <c r="B170" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C170" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D170" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E170" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F170" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G170" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H170" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning canton ga</t>
+        </is>
+      </c>
+      <c r="B171" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C171" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D171" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F171" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G171" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H171" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning farmington</t>
+        </is>
+      </c>
+      <c r="B172" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C172" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D172" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F172" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G172" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H172" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning jackson mi</t>
+        </is>
+      </c>
+      <c r="B173" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C173" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D173" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G173" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H173" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning michigan</t>
+        </is>
+      </c>
+      <c r="B174" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C174" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F174" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G174" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H174" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning midland</t>
+        </is>
+      </c>
+      <c r="B175" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C175" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G175" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H175" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning muskegon</t>
+        </is>
+      </c>
+      <c r="B176" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C176" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D176" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F176" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G176" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H176" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning near</t>
+        </is>
+      </c>
+      <c r="B177" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C177" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F177" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G177" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H177" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning near me coupons</t>
+        </is>
+      </c>
+      <c r="B178" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C178" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D178" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F178" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G178" s="17" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H178" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning pet stains</t>
+        </is>
+      </c>
+      <c r="B179" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C179" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F179" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G179" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H179" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning quote online</t>
+        </is>
+      </c>
+      <c r="B180" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C180" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F180" s="17" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="G180" s="17" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="H180" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning rockford</t>
+        </is>
+      </c>
+      <c r="B181" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C181" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D181" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F181" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G181" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H181" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning royal oak</t>
+        </is>
+      </c>
+      <c r="B182" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C182" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D182" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F182" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G182" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H182" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning saginaw mi</t>
+        </is>
+      </c>
+      <c r="B183" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C183" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D183" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F183" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G183" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H183" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning sterling heights mi</t>
+        </is>
+      </c>
+      <c r="B184" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C184" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D184" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E184" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F184" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G184" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H184" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleaning today</t>
+        </is>
+      </c>
+      <c r="B185" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C185" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D185" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E185" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F185" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G185" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H185" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="17" t="inlineStr">
+        <is>
+          <t>carpet cleaning website</t>
+        </is>
+      </c>
+      <c r="B186" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C186" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E186" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F186" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G186" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H186" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="21" t="inlineStr">
+        <is>
+          <t>carpet cleanner</t>
+        </is>
+      </c>
+      <c r="B187" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C187" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="D187" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G187" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H187" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="17" t="inlineStr">
+        <is>
+          <t>carpet steamer company</t>
+        </is>
+      </c>
+      <c r="B188" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C188" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F188" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G188" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H188" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="21" t="inlineStr">
+        <is>
+          <t>carpet technician</t>
+        </is>
+      </c>
+      <c r="B189" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C189" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="D189" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F189" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G189" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H189" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="17" t="inlineStr">
+        <is>
+          <t>carpet washing services</t>
+        </is>
+      </c>
+      <c r="B190" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C190" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D190" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E190" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F190" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G190" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H190" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="21" t="inlineStr">
+        <is>
+          <t>carpet. cleaner</t>
+        </is>
+      </c>
+      <c r="B191" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C191" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D191" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E191" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F191" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G191" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H191" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="17" t="inlineStr">
+        <is>
+          <t>carpets cleaners</t>
+        </is>
+      </c>
+      <c r="B192" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C192" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E192" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F192" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G192" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H192" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="21" t="inlineStr">
+        <is>
+          <t>cleaning coupon</t>
+        </is>
+      </c>
+      <c r="B193" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C193" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D193" s="26" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>Carpet &amp; Upholstery</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E193" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F193" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G193" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H193" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="17" t="inlineStr">
+        <is>
+          <t>commercial carpet clean</t>
+        </is>
+      </c>
+      <c r="B194" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C194" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D194" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E194" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F194" s="17" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G194" s="17" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>rug cleaning near me</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12100</v>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="H194" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="21" t="inlineStr">
+        <is>
+          <t>commercial carpet cleaning brighton</t>
+        </is>
+      </c>
+      <c r="B195" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C195" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D195" s="26" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F195" s="21" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="G195" s="21" t="inlineStr">
         <is>
           <t>Bottom of funnel</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>area rug cleaning near me</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5400</v>
-      </c>
-      <c r="C5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="H195" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="17" t="inlineStr">
+        <is>
+          <t>companies that clean carpets</t>
+        </is>
+      </c>
+      <c r="B196" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C196" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D196" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F196" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G196" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H196" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="21" t="inlineStr">
+        <is>
+          <t>company to clean carpet</t>
+        </is>
+      </c>
+      <c r="B197" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C197" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="D197" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E197" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F197" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G197" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H197" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="17" t="inlineStr">
+        <is>
+          <t>fenton carpet cleaning fenton mi</t>
+        </is>
+      </c>
+      <c r="B198" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C198" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D198" s="26" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>drapery cleaning</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="E198" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F198" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G198" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H198" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="21" t="inlineStr">
+        <is>
+          <t>house carpet cleaning services</t>
+        </is>
+      </c>
+      <c r="B199" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C199" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="D199" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E199" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F199" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G199" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H199" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="17" t="inlineStr">
+        <is>
+          <t>how often can you clean carpets</t>
+        </is>
+      </c>
+      <c r="B200" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C200" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D200" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F200" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G200" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H200" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="21" t="inlineStr">
+        <is>
+          <t>how often should you clean a carpet</t>
+        </is>
+      </c>
+      <c r="B201" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C201" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D201" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E201" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F201" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G201" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H201" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="17" t="inlineStr">
+        <is>
+          <t>how often should you get your carpets cleaned</t>
+        </is>
+      </c>
+      <c r="B202" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C202" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D202" s="26" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F202" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G202" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H202" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="21" t="inlineStr">
+        <is>
+          <t>how often should you have carpet professionally cleaned</t>
+        </is>
+      </c>
+      <c r="B203" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C203" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D203" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E203" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F203" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G203" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H203" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="17" t="inlineStr">
+        <is>
+          <t>how often should you have your carpet cleaned</t>
+        </is>
+      </c>
+      <c r="B204" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C204" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D204" s="26" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F204" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G204" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H204" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="21" t="inlineStr">
+        <is>
+          <t>local carpet cleaning company</t>
+        </is>
+      </c>
+      <c r="B205" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C205" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D205" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E205" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F205" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G205" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H205" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="17" t="inlineStr">
+        <is>
+          <t>professional carpet cleaning companies</t>
+        </is>
+      </c>
+      <c r="B206" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C206" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="D206" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E206" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F206" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G206" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H206" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="21" t="inlineStr">
+        <is>
+          <t>professional carpet cleaning services richland county</t>
+        </is>
+      </c>
+      <c r="B207" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C207" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D207" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E207" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F207" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G207" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H207" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="17" t="inlineStr">
+        <is>
+          <t>professional steam cleaning services</t>
+        </is>
+      </c>
+      <c r="B208" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C208" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D208" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E208" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F208" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G208" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H208" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="21" t="inlineStr">
+        <is>
+          <t>professional tile and grout cleaning cost</t>
+        </is>
+      </c>
+      <c r="B209" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C209" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" s="28" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E209" s="25" t="inlineStr">
         <is>
           <t>Drapery &amp; Specialty</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>upholstery cleaning</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="F209" s="21" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="G209" s="21" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="H209" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="17" t="inlineStr">
+        <is>
+          <t>sectional cleaning</t>
+        </is>
+      </c>
+      <c r="B210" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C210" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D210" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E210" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F210" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G210" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H210" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="21" t="inlineStr">
+        <is>
+          <t>upholstery cleaned</t>
+        </is>
+      </c>
+      <c r="B211" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C211" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D211" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F211" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G211" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H211" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="17" t="inlineStr">
+        <is>
+          <t>what carpet cleaning company is the best</t>
+        </is>
+      </c>
+      <c r="B212" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C212" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D212" s="18" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E212" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F212" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G212" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H212" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="21" t="inlineStr">
+        <is>
+          <t>what is carpet cleaning</t>
+        </is>
+      </c>
+      <c r="B213" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C213" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D213" s="24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Carpet &amp; Upholstery</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>hardwood floor refinishing</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>9900</v>
-      </c>
-      <c r="C8" t="n">
-        <v>32</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="E213" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F213" s="21" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G213" s="21" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H213" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="17" t="inlineStr">
+        <is>
+          <t>who cleans furniture</t>
+        </is>
+      </c>
+      <c r="B214" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="C214" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D214" s="24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Drapery &amp; Specialty</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tile grout cleaning</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C9" t="n">
-        <v>22</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Drapery &amp; Specialty</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>carpet stain removal</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>12100</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Carpet &amp; Upholstery</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pet odor removal carpet</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Carpet &amp; Upholstery</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Middle of funnel</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>carpet cleaning rockville md</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>rug cleaning bethesda</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>720</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rug cleaning silver spring</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>590</v>
-      </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>country squire cleaners</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>590</v>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Competitor</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Branded</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Middle of funnel</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No — competitor brand; suppress via site audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>carpet cleaning bethesda md</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>880</v>
-      </c>
-      <c r="C16" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>carpet cleaning kensington md</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>390</v>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>rug cleaning potomac md</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>260</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Location Authority</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>wool rug cleaning</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C19" t="n">
-        <v>24</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>silk rug cleaning</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Middle of funnel</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>persian rug cleaning</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C21" t="n">
-        <v>26</v>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Oriental &amp; Specialty Rugs</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="E214" s="19" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Upholstery</t>
+        </is>
+      </c>
+      <c r="F214" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="G214" s="17" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="H214" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
